--- a/Sales Results/SalesResults-2026-10-18.xlsx
+++ b/Sales Results/SalesResults-2026-10-18.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fabio\Documents\UIPATH\Execel_Consolidação\Sales Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA36F739-29DB-458A-AF48-C2DAF06DFE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C552C4D2-4A68-40FD-9CCF-B90AEECC228C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FFD71BB3-DA32-4757-8E8D-38F9E5E28FA5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1334C4D4-FA1D-4C76-9150-19E62377DE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Novos Valores" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="181" r:id="rId4"/>
+    <pivotCache cacheId="321" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="18">
   <si>
     <t>Item</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Sum of 66</t>
+  </si>
+  <si>
+    <t>FlatWhite</t>
   </si>
 </sst>
 </file>
@@ -262,7 +265,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-21A3-44B9-AB01-3F4C9501C6AE}"/>
+              <c16:uniqueId val="{00000000-0512-4F72-8041-2F7E384D3857}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -337,7 +340,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{373A5ADA-80BF-33F1-C47A-FA6FDDB80D48}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A785189F-8240-5CCE-5600-CE785790694B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -359,7 +362,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Fabio" refreshedDate="46313.555222453702" createdVersion="1" refreshedVersion="8" recordCount="4" xr:uid="{58BDEB07-EFF0-4FCB-A469-D8CF2B66FEDF}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Fabio" refreshedDate="46313.902257870373" createdVersion="1" refreshedVersion="8" recordCount="4" xr:uid="{AA6B8F0E-1576-4394-B261-25EB66E104B2}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D5" sheet="Novos Valores"/>
   </cacheSource>
@@ -420,7 +423,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D37EC2DA-E551-4B0B-9804-896C9F8DEF9A}" name="Grafico" cacheId="181" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5D8B64E9-CD94-4B34-82BF-D7790492A741}" name="Grafico" cacheId="321" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Data" updatedVersion="8" asteriskTotals="1" showMultipleLabel="0" showMemberPropertyTips="0" useAutoFormatting="1" itemPrintTitles="1" showDropZones="0" indent="0" outline="1" outlineData="1" chartFormat="1">
   <location ref="A1:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
@@ -804,8 +807,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0843311F-E9D9-4D33-9D12-49A0700DA1ED}">
-  <dimension ref="A1:D40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3ED1FF4-4CE0-4510-9ACD-17A88A904324}">
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -956,10 +959,10 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D11">
-        <v>156</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -970,10 +973,10 @@
         <v>3</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>36</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1012,24 +1015,24 @@
         <v>4.5</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D15">
-        <v>63</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>4.5</v>
       </c>
       <c r="C16">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D16">
-        <v>99</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1040,10 +1043,10 @@
         <v>4.5</v>
       </c>
       <c r="C17">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="D17">
-        <v>553.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1054,10 +1057,10 @@
         <v>4</v>
       </c>
       <c r="C18">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D18">
-        <v>124</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1068,10 +1071,10 @@
         <v>3</v>
       </c>
       <c r="C19">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1082,10 +1085,10 @@
         <v>3.5</v>
       </c>
       <c r="C20">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D20">
-        <v>231</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1096,10 +1099,10 @@
         <v>3</v>
       </c>
       <c r="C21">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D21">
-        <v>114</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1124,10 +1127,10 @@
         <v>3.5</v>
       </c>
       <c r="C23">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D23">
-        <v>154</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1152,10 +1155,10 @@
         <v>4.5</v>
       </c>
       <c r="C25">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="D25">
-        <v>603</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1166,10 +1169,10 @@
         <v>4.5</v>
       </c>
       <c r="C26">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="D26">
-        <v>225</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1180,10 +1183,10 @@
         <v>4.5</v>
       </c>
       <c r="C27">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="D27">
-        <v>189</v>
+        <v>553.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1194,10 +1197,10 @@
         <v>4</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D28">
-        <v>48</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1208,10 +1211,10 @@
         <v>3</v>
       </c>
       <c r="C29">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="D29">
-        <v>189</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1222,10 +1225,10 @@
         <v>3.5</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="D30">
-        <v>35</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1236,10 +1239,10 @@
         <v>3</v>
       </c>
       <c r="C31">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="D31">
-        <v>222</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1250,10 +1253,10 @@
         <v>3</v>
       </c>
       <c r="C32">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D32">
-        <v>69</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1264,10 +1267,10 @@
         <v>3.5</v>
       </c>
       <c r="C33">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D33">
-        <v>77</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1278,10 +1281,10 @@
         <v>4</v>
       </c>
       <c r="C34">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D34">
-        <v>52</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1292,10 +1295,10 @@
         <v>4.5</v>
       </c>
       <c r="C35">
-        <v>22</v>
+        <v>134</v>
       </c>
       <c r="D35">
-        <v>99</v>
+        <v>603</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1306,10 +1309,10 @@
         <v>4.5</v>
       </c>
       <c r="C36">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D36">
-        <v>288</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1320,10 +1323,10 @@
         <v>4.5</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D37">
-        <v>45</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1334,10 +1337,10 @@
         <v>4</v>
       </c>
       <c r="C38">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D38">
-        <v>88</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1348,10 +1351,10 @@
         <v>3</v>
       </c>
       <c r="C39">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D39">
-        <v>93</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1362,9 +1365,149 @@
         <v>3.5</v>
       </c>
       <c r="C40">
+        <v>10</v>
+      </c>
+      <c r="D40">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41">
+        <v>3</v>
+      </c>
+      <c r="C41">
+        <v>74</v>
+      </c>
+      <c r="D41">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42">
+        <v>3</v>
+      </c>
+      <c r="C42">
+        <v>23</v>
+      </c>
+      <c r="D42">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43">
+        <v>3.5</v>
+      </c>
+      <c r="C43">
+        <v>22</v>
+      </c>
+      <c r="D43">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44">
+        <v>4</v>
+      </c>
+      <c r="C44">
+        <v>13</v>
+      </c>
+      <c r="D44">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45">
+        <v>4.5</v>
+      </c>
+      <c r="C45">
+        <v>22</v>
+      </c>
+      <c r="D45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46">
+        <v>4.5</v>
+      </c>
+      <c r="C46">
+        <v>64</v>
+      </c>
+      <c r="D46">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47">
+        <v>4.5</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>22</v>
+      </c>
+      <c r="D48">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49">
+        <v>31</v>
+      </c>
+      <c r="D49">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50">
+        <v>3.5</v>
+      </c>
+      <c r="C50">
         <v>20</v>
       </c>
-      <c r="D40">
+      <c r="D50">
         <v>70</v>
       </c>
     </row>
@@ -1374,7 +1517,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9D45566-925A-4226-9484-713AD1683A2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{070DD45C-FDD1-47CF-8425-87A929DB1142}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1437,7 +1580,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FFA30C7-6723-4C04-924F-B5010D7EF37F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4E3A11-E4D4-4F46-B765-25FDBB4AB042}">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
